--- a/5월 자금유출입.xlsx
+++ b/5월 자금유출입.xlsx
@@ -141,6 +141,9 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">콜머니(+)</t>
+  </si>
+  <si>
     <t xml:space="preserve">당일 마감액</t>
   </si>
   <si>
@@ -205,87 +208,71 @@
     <t xml:space="preserve">합계</t>
   </si>
   <si>
-    <t xml:space="preserve">※ 당발·타발송금은 고객 거래에 따라 예측이 불가능한 금액이며, FX거래 자금유출입은 전일자·당일 마감액의 차이로 산출됨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 노란색 칸(전일자 마감액·당일 마감액)에 값을 입력하면 FX거래 자금유출입이 자동 계산됩니다.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
+    <r>
+      <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 콜머니제외 마감액 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FFC00000"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">※ FX</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">실제 가용 가능했던 여유자금 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">거래 자금유출입 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">강조 표시</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+      <t xml:space="preserve">당일 마감액 − 전일자 마감액 </t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
-        <color rgb="FFC00000"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
+      <t xml:space="preserve">+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">당발송금 − 타발송금 − 콜머니</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 노란색 칸(전일자 마감액·콜머니·당일 마감액)에 값을 입력하면 FX거래 자금유출입이 자동 계산됩니다. (콜머니 없는 날은 비워두면 0으로 처리)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,50 +353,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF0000FF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -419,25 +370,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAD3"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4B183"/>
-        <bgColor rgb="FFFF99CC"/>
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -457,40 +402,24 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FFC00000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFC00000"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFC00000"/>
-      </top>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FFC00000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFC00000"/>
-      </right>
+      <left style="medium"/>
+      <right style="medium"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="thick">
-        <color rgb="FFC00000"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFC00000"/>
-      </right>
+      <left style="medium"/>
+      <right style="medium"/>
       <top style="thin"/>
-      <bottom style="thick">
-        <color rgb="FFC00000"/>
-      </bottom>
+      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -519,7 +448,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -544,7 +473,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -560,7 +489,7 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -568,19 +497,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -596,8 +521,8 @@
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -618,7 +543,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFBDD7EE"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -634,7 +559,7 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF4B183"/>
+      <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -836,20 +761,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -872,13 +798,16 @@
       <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="9" t="n">
@@ -888,15 +817,16 @@
         <v>18.13</v>
       </c>
       <c r="E4" s="9" t="str">
-        <f aca="false">IF(OR(B4="",F4=""),"",F4-B4+C4-D4)</f>
+        <f aca="false">IF(OR(B4="",G4=""),"",G4-B4+C4-D4-F4)</f>
         <v/>
       </c>
       <c r="F4" s="8"/>
-      <c r="G4" s="10"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="9" t="n">
@@ -906,15 +836,16 @@
         <v>28.15</v>
       </c>
       <c r="E5" s="9" t="str">
-        <f aca="false">IF(OR(B5="",F5=""),"",F5-B5+C5-D5)</f>
+        <f aca="false">IF(OR(B5="",G5=""),"",G5-B5+C5-D5-F5)</f>
         <v/>
       </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="10"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="n">
@@ -924,15 +855,16 @@
         <v>27.93</v>
       </c>
       <c r="E6" s="9" t="str">
-        <f aca="false">IF(OR(B6="",F6=""),"",F6-B6+C6-D6)</f>
+        <f aca="false">IF(OR(B6="",G6=""),"",G6-B6+C6-D6-F6)</f>
         <v/>
       </c>
       <c r="F6" s="8"/>
-      <c r="G6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="n">
@@ -942,15 +874,16 @@
         <v>24.52</v>
       </c>
       <c r="E7" s="9" t="str">
-        <f aca="false">IF(OR(B7="",F7=""),"",F7-B7+C7-D7)</f>
+        <f aca="false">IF(OR(B7="",G7=""),"",G7-B7+C7-D7-F7)</f>
         <v/>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="10"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="n">
@@ -960,15 +893,16 @@
         <v>16.65</v>
       </c>
       <c r="E8" s="9" t="str">
-        <f aca="false">IF(OR(B8="",F8=""),"",F8-B8+C8-D8)</f>
+        <f aca="false">IF(OR(B8="",G8=""),"",G8-B8+C8-D8-F8)</f>
         <v/>
       </c>
       <c r="F8" s="8"/>
-      <c r="G8" s="10"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="n">
@@ -978,15 +912,16 @@
         <v>24.55</v>
       </c>
       <c r="E9" s="9" t="str">
-        <f aca="false">IF(OR(B9="",F9=""),"",F9-B9+C9-D9)</f>
+        <f aca="false">IF(OR(B9="",G9=""),"",G9-B9+C9-D9-F9)</f>
         <v/>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="10"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="9" t="n">
@@ -996,15 +931,16 @@
         <v>13.9</v>
       </c>
       <c r="E10" s="9" t="str">
-        <f aca="false">IF(OR(B10="",F10=""),"",F10-B10+C10-D10)</f>
+        <f aca="false">IF(OR(B10="",G10=""),"",G10-B10+C10-D10-F10)</f>
         <v/>
       </c>
       <c r="F10" s="8"/>
-      <c r="G10" s="10"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="9" t="n">
@@ -1014,15 +950,16 @@
         <v>51.75</v>
       </c>
       <c r="E11" s="9" t="str">
-        <f aca="false">IF(OR(B11="",F11=""),"",F11-B11+C11-D11)</f>
+        <f aca="false">IF(OR(B11="",G11=""),"",G11-B11+C11-D11-F11)</f>
         <v/>
       </c>
       <c r="F11" s="8"/>
-      <c r="G11" s="10"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="9" t="n">
@@ -1032,15 +969,16 @@
         <v>46.1</v>
       </c>
       <c r="E12" s="9" t="str">
-        <f aca="false">IF(OR(B12="",F12=""),"",F12-B12+C12-D12)</f>
+        <f aca="false">IF(OR(B12="",G12=""),"",G12-B12+C12-D12-F12)</f>
         <v/>
       </c>
       <c r="F12" s="8"/>
-      <c r="G12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="9" t="n">
@@ -1050,15 +988,16 @@
         <v>25.13</v>
       </c>
       <c r="E13" s="9" t="str">
-        <f aca="false">IF(OR(B13="",F13=""),"",F13-B13+C13-D13)</f>
+        <f aca="false">IF(OR(B13="",G13=""),"",G13-B13+C13-D13-F13)</f>
         <v/>
       </c>
       <c r="F13" s="8"/>
-      <c r="G13" s="10"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="9" t="n">
@@ -1068,15 +1007,16 @@
         <v>16.44</v>
       </c>
       <c r="E14" s="9" t="str">
-        <f aca="false">IF(OR(B14="",F14=""),"",F14-B14+C14-D14)</f>
+        <f aca="false">IF(OR(B14="",G14=""),"",G14-B14+C14-D14-F14)</f>
         <v/>
       </c>
       <c r="F14" s="8"/>
-      <c r="G14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="9" t="n">
@@ -1086,15 +1026,16 @@
         <v>20.77</v>
       </c>
       <c r="E15" s="9" t="str">
-        <f aca="false">IF(OR(B15="",F15=""),"",F15-B15+C15-D15)</f>
+        <f aca="false">IF(OR(B15="",G15=""),"",G15-B15+C15-D15-F15)</f>
         <v/>
       </c>
       <c r="F15" s="8"/>
-      <c r="G15" s="10"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="9" t="n">
@@ -1104,15 +1045,16 @@
         <v>40.43</v>
       </c>
       <c r="E16" s="9" t="str">
-        <f aca="false">IF(OR(B16="",F16=""),"",F16-B16+C16-D16)</f>
+        <f aca="false">IF(OR(B16="",G16=""),"",G16-B16+C16-D16-F16)</f>
         <v/>
       </c>
       <c r="F16" s="8"/>
-      <c r="G16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="9" t="n">
@@ -1122,15 +1064,16 @@
         <v>120.41</v>
       </c>
       <c r="E17" s="9" t="str">
-        <f aca="false">IF(OR(B17="",F17=""),"",F17-B17+C17-D17)</f>
+        <f aca="false">IF(OR(B17="",G17=""),"",G17-B17+C17-D17-F17)</f>
         <v/>
       </c>
       <c r="F17" s="8"/>
-      <c r="G17" s="10"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="9" t="n">
@@ -1140,15 +1083,16 @@
         <v>37.7</v>
       </c>
       <c r="E18" s="9" t="str">
-        <f aca="false">IF(OR(B18="",F18=""),"",F18-B18+C18-D18)</f>
+        <f aca="false">IF(OR(B18="",G18=""),"",G18-B18+C18-D18-F18)</f>
         <v/>
       </c>
       <c r="F18" s="8"/>
-      <c r="G18" s="10"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="9" t="n">
@@ -1158,15 +1102,16 @@
         <v>42.6</v>
       </c>
       <c r="E19" s="9" t="str">
-        <f aca="false">IF(OR(B19="",F19=""),"",F19-B19+C19-D19)</f>
+        <f aca="false">IF(OR(B19="",G19=""),"",G19-B19+C19-D19-F19)</f>
         <v/>
       </c>
       <c r="F19" s="8"/>
-      <c r="G19" s="10"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="9" t="n">
@@ -1176,15 +1121,16 @@
         <v>8.3</v>
       </c>
       <c r="E20" s="9" t="str">
-        <f aca="false">IF(OR(B20="",F20=""),"",F20-B20+C20-D20)</f>
+        <f aca="false">IF(OR(B20="",G20=""),"",G20-B20+C20-D20-F20)</f>
         <v/>
       </c>
       <c r="F20" s="8"/>
-      <c r="G20" s="10"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="8"/>
       <c r="C21" s="9" t="n">
@@ -1194,18 +1140,19 @@
         <v>57.45</v>
       </c>
       <c r="E21" s="9" t="str">
-        <f aca="false">IF(OR(B21="",F21=""),"",F21-B21+C21-D21)</f>
+        <f aca="false">IF(OR(B21="",G21=""),"",G21-B21+C21-D21-F21)</f>
         <v/>
       </c>
       <c r="F21" s="8"/>
-      <c r="G21" s="10"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="11" t="str">
-        <f aca="false">IF(SUM(B4:B21)=0,"",SUM(B4:B21))</f>
+        <f aca="false">IF(COUNT(B4:B21)=0,"",SUM(B4:B21))</f>
         <v/>
       </c>
       <c r="C22" s="11" t="n">
@@ -1217,30 +1164,29 @@
         <v>620.91</v>
       </c>
       <c r="E22" s="11" t="str">
-        <f aca="false">IF(SUM(B4:B21)=0,"",SUM(E4:E21))</f>
+        <f aca="false">IF(COUNT(E4:E21)=0,"",SUM(E4:E21))</f>
         <v/>
       </c>
       <c r="F22" s="11" t="str">
-        <f aca="false">IF(SUM(F4:F21)=0,"",SUM(F4:F21))</f>
-        <v/>
-      </c>
-      <c r="G22" s="12" t="str">
-        <f aca="false">IF(SUM(G4:G21)=0,"",SUM(G4:G21))</f>
+        <f aca="false">IF(COUNT(F4:F21)=0,"",SUM(F4:F21))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11" t="str">
+        <f aca="false">IF(COUNT(G4:G21)=0,"",SUM(G4:G21))</f>
+        <v/>
+      </c>
+      <c r="H22" s="12" t="str">
+        <f aca="false">IF(COUNT(H4:H21)=0,"",SUM(H4:H21))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
         <v>30</v>
       </c>
     </row>
